--- a/artfynd/A 45113-2022 artfynd.xlsx
+++ b/artfynd/A 45113-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 45113-2022 artfynd.xlsx
+++ b/artfynd/A 45113-2022 artfynd.xlsx
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>67751504</v>
+        <v>79912867</v>
       </c>
       <c r="B2" t="n">
-        <v>90138</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>88953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Violett fingersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Clavaria amethystina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Holmsk.) Bull.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -719,19 +714,20 @@
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fasterna, Kronberg 250 m NV, Upl</t>
+          <t>Fasterna, Kronberg 250 m NNV, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>686492.95932522</v>
+        <v>686441</v>
       </c>
       <c r="R2" t="n">
-        <v>6631889.36987605</v>
+        <v>6631885</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,22 +751,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-09-30</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-09-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Sporer färglösa, subglobosa, ca 4-5 x 4 µm, 4 sp/basidium. Hyfer utan söljor.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,12 +776,22 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Lövskog</t>
+          <t>Aspskog</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>på fallen aspstam</t>
+          <t>Igenväxande, mullrik hagmark med asp och hassel.</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>Stockholm-Naturhistoriska riksmuseet</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>F372335</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -801,49 +802,44 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rikard Anderberg, Arne Anderberg</t>
+          <t>Arne Anderberg, Rikard Anderberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>79912867</v>
+        <v>67751504</v>
       </c>
       <c r="B3" t="n">
-        <v>84993</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violett fingersvamp</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Clavaria zollingeri</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Lév.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -852,20 +848,19 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fasterna, Kronberg 250 m NNV, Upl</t>
+          <t>Fasterna, Kronberg 250 m NV, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>686441.1309810055</v>
+        <v>686493</v>
       </c>
       <c r="R3" t="n">
-        <v>6631885.25711967</v>
+        <v>6631889</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,27 +884,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Sporer färglösa, subglobosa, ca 4-5 x 4 µm, 4 sp/basidium. Hyfer utan söljor.</t>
+          <t>2017-09-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,22 +904,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Aspskog</t>
+          <t>Lövskog</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Igenväxande, mullrik hagmark med asp och hassel.</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>Stockholm-Naturhistoriska riksmuseet</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>F372335</t>
+          <t>på fallen aspstam</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -960,12 +930,7 @@
         <v>79912942</v>
       </c>
       <c r="B4" t="n">
-        <v>77870</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79699</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,10 +977,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>686457.2810125866</v>
+        <v>686457</v>
       </c>
       <c r="R4" t="n">
-        <v>6631895.649399449</v>
+        <v>6631896</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1045,19 +1010,9 @@
           <t>2019-09-14</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-09-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1113,7 +1068,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Rikard Anderberg, Arne Anderberg</t>
+          <t>Arne Anderberg, Rikard Anderberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 45113-2022 artfynd.xlsx
+++ b/artfynd/A 45113-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -806,6 +811,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79912867</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -924,6 +934,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67751504</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1072,8 +1087,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79912942</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>